--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1361" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B180EB-BEC6-40C2-A9D3-BE0EC3669F23}"/>
+  <xr:revisionPtr revIDLastSave="1363" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54B81C01-2C53-4623-BD08-7E66D7F8F3C5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="SegmentaciónDeDatos_Sitio">#N/A</definedName>
     <definedName name="SegmentaciónDeDatos_Unidad">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="125">
   <si>
     <t>ID</t>
   </si>
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -513,11 +513,24 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -548,16 +561,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -850,23 +853,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J348" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A10:J348" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J349" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J349" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="3" xr3:uid="{AFE823F6-980E-4E32-B4F4-6ECDE10F377D}" name="ID"/>
-    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="9">
       <calculatedColumnFormula>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{C2DE1A32-EBAC-4C95-A60E-FB6BAE643966}" name="Verificación"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -894,9 +897,9 @@
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1EEE0FFC-B699-4850-9A13-72CF6FB78CA6}" name="Unidad"/>
-    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{E5C19B72-F1F0-4F1D-9466-99048BCEFC0C}" name="Motivo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1232,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J348"/>
+  <dimension ref="A9:J349"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1251,7 +1254,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10514,6 +10517,24 @@
       <c r="J348" s="1" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>339</v>
+      </c>
+      <c r="B349" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C349" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D349" s="14"/>
+      <c r="E349" s="13"/>
+      <c r="F349" s="15"/>
+      <c r="G349" s="15"/>
+      <c r="H349" s="11"/>
+      <c r="I349" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11017,6 +11038,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -11219,30 +11263,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11261,24 +11300,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1363" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54B81C01-2C53-4623-BD08-7E66D7F8F3C5}"/>
+  <xr:revisionPtr revIDLastSave="1369" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15DF394F-0787-4BD6-A052-F4C7FEDF6AB3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="127">
   <si>
     <t>ID</t>
   </si>
@@ -429,6 +429,12 @@
   </si>
   <si>
     <t>FechaFinVigencia</t>
+  </si>
+  <si>
+    <t>Retiro controlado TV</t>
+  </si>
+  <si>
+    <t>Alarma alta presión sistema de lubricación.</t>
   </si>
 </sst>
 </file>
@@ -10529,12 +10535,24 @@
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
-      <c r="D349" s="14"/>
-      <c r="E349" s="13"/>
-      <c r="F349" s="15"/>
-      <c r="G349" s="15"/>
-      <c r="H349" s="11"/>
-      <c r="I349" s="11"/>
+      <c r="D349" s="14">
+        <v>262</v>
+      </c>
+      <c r="E349" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F349" s="15">
+        <v>46270.692361111112</v>
+      </c>
+      <c r="G349" s="15">
+        <v>46271.84375</v>
+      </c>
+      <c r="H349" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I349" s="11" t="s">
+        <v>126</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1369" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15DF394F-0787-4BD6-A052-F4C7FEDF6AB3}"/>
+  <xr:revisionPtr revIDLastSave="1375" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55DA9378-69C5-43E9-9D0F-6FE80772344B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="127">
   <si>
     <t>ID</t>
   </si>
@@ -859,8 +859,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J349" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J349" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J350" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J350" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1241,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J349"/>
+  <dimension ref="A9:J350"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1260,7 +1260,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10525,7 +10525,7 @@
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A349">
+      <c r="A349" s="1">
         <v>339</v>
       </c>
       <c r="B349" s="13" t="s">
@@ -10553,6 +10553,24 @@
       <c r="I349" s="11" t="s">
         <v>126</v>
       </c>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
+        <v>340</v>
+      </c>
+      <c r="B350" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C350" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D350" s="14"/>
+      <c r="E350" s="13"/>
+      <c r="F350" s="15"/>
+      <c r="G350" s="15"/>
+      <c r="H350" s="11"/>
+      <c r="I350" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1375" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55DA9378-69C5-43E9-9D0F-6FE80772344B}"/>
+  <xr:revisionPtr revIDLastSave="1380" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2443CB7-8F3D-4227-9B1F-0D74CA36E357}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="128">
   <si>
     <t>ID</t>
   </si>
@@ -435,6 +435,9 @@
   </si>
   <si>
     <t>Alarma alta presión sistema de lubricación.</t>
+  </si>
+  <si>
+    <t>Alta vibración descanzo TV</t>
   </si>
 </sst>
 </file>
@@ -10565,12 +10568,22 @@
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
-      <c r="D350" s="14"/>
-      <c r="E350" s="13"/>
-      <c r="F350" s="15"/>
+      <c r="D350" s="14">
+        <v>262</v>
+      </c>
+      <c r="E350" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F350" s="15">
+        <v>46275.823611111111</v>
+      </c>
       <c r="G350" s="15"/>
-      <c r="H350" s="11"/>
-      <c r="I350" s="11"/>
+      <c r="H350" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I350" s="11" t="s">
+        <v>127</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1380" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2443CB7-8F3D-4227-9B1F-0D74CA36E357}"/>
+  <xr:revisionPtr revIDLastSave="1381" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A02F838D-9365-469C-96DD-6279E7ED5F8D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -10577,7 +10577,9 @@
       <c r="F350" s="15">
         <v>46275.823611111111</v>
       </c>
-      <c r="G350" s="15"/>
+      <c r="G350" s="15">
+        <v>46275.894444444442</v>
+      </c>
       <c r="H350" s="11" t="s">
         <v>125</v>
       </c>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1381" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A02F838D-9365-469C-96DD-6279E7ED5F8D}"/>
+  <xr:revisionPtr revIDLastSave="1403" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{267F2563-5D3F-4A31-8E4D-E27562715331}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="130">
   <si>
     <t>ID</t>
   </si>
@@ -438,6 +438,12 @@
   </si>
   <si>
     <t>Alta vibración descanzo TV</t>
+  </si>
+  <si>
+    <t>Bajo nivel del Domo MP</t>
+  </si>
+  <si>
+    <t>Falla valvúla control nivel del Domo MP</t>
   </si>
 </sst>
 </file>
@@ -862,8 +868,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J350" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J350" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J352" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J352" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1244,7 +1250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J350"/>
+  <dimension ref="A9:J352"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1263,7 +1269,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10584,6 +10590,66 @@
         <v>125</v>
       </c>
       <c r="I350" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
+        <v>341</v>
+      </c>
+      <c r="B351" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C351" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CEM</v>
+      </c>
+      <c r="D351" s="14">
+        <v>0</v>
+      </c>
+      <c r="E351" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F351" s="15">
+        <v>46276.121527777781</v>
+      </c>
+      <c r="G351" s="15">
+        <v>46276.189583333333</v>
+      </c>
+      <c r="H351" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="I351" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
+        <v>342</v>
+      </c>
+      <c r="B352" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C352" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D352" s="14">
+        <v>262</v>
+      </c>
+      <c r="E352" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F352" s="15">
+        <v>46277.865277777775</v>
+      </c>
+      <c r="G352" s="15">
+        <v>46277.884027777778</v>
+      </c>
+      <c r="H352" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I352" s="11" t="s">
         <v>127</v>
       </c>
     </row>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1403" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{267F2563-5D3F-4A31-8E4D-E27562715331}"/>
+  <xr:revisionPtr revIDLastSave="1408" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EBF5C0F-4D67-4F27-A808-ADE0DC9A8803}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -868,8 +868,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J352" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A10:J352" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J353" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A10:J353" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1250,7 +1250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J352"/>
+  <dimension ref="A9:J353"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -10652,6 +10652,16 @@
       <c r="I352" s="11" t="s">
         <v>127</v>
       </c>
+    </row>
+    <row r="353" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B353" s="13"/>
+      <c r="C353" s="16"/>
+      <c r="D353" s="14"/>
+      <c r="E353" s="13"/>
+      <c r="F353" s="15"/>
+      <c r="G353" s="15"/>
+      <c r="H353" s="11"/>
+      <c r="I353" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1408" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EBF5C0F-4D67-4F27-A808-ADE0DC9A8803}"/>
+  <xr:revisionPtr revIDLastSave="1410" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{304DBD10-59C9-4C14-8DB7-3F4C0452196D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="130">
   <si>
     <t>ID</t>
   </si>
@@ -10521,7 +10521,7 @@
         <v>46262.939583333333</v>
       </c>
       <c r="G348" s="15">
-        <v>46250.243750000001</v>
+        <v>46263.368750000001</v>
       </c>
       <c r="H348" s="11" t="s">
         <v>110</v>
@@ -10562,6 +10562,9 @@
       <c r="I349" s="11" t="s">
         <v>126</v>
       </c>
+      <c r="J349" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
@@ -10592,6 +10595,9 @@
       <c r="I350" s="11" t="s">
         <v>127</v>
       </c>
+      <c r="J350" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
@@ -10622,6 +10628,9 @@
       <c r="I351" s="11" t="s">
         <v>129</v>
       </c>
+      <c r="J351" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
@@ -10651,6 +10660,9 @@
       </c>
       <c r="I352" s="11" t="s">
         <v>127</v>
+      </c>
+      <c r="J352" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="353" spans="2:9" x14ac:dyDescent="0.25">

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1410" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{304DBD10-59C9-4C14-8DB7-3F4C0452196D}"/>
+  <xr:revisionPtr revIDLastSave="1412" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1717139-AF42-45E9-8CDD-DA50C4838550}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -487,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -526,9 +526,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -10540,7 +10537,7 @@
       <c r="B349" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C349" s="16" t="str">
+      <c r="C349" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10573,7 +10570,7 @@
       <c r="B350" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C350" s="16" t="str">
+      <c r="C350" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10606,7 +10603,7 @@
       <c r="B351" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C351" s="16" t="str">
+      <c r="C351" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CEM</v>
       </c>
@@ -10639,7 +10636,7 @@
       <c r="B352" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C352" s="16" t="str">
+      <c r="C352" s="13" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
@@ -10667,7 +10664,7 @@
     </row>
     <row r="353" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B353" s="13"/>
-      <c r="C353" s="16"/>
+      <c r="C353" s="13"/>
       <c r="D353" s="14"/>
       <c r="E353" s="13"/>
       <c r="F353" s="15"/>
@@ -10898,10 +10895,11 @@
         <v>46023</v>
       </c>
       <c r="C2" s="3">
-        <v>46254.999988425923</v>
+        <v>46295.999988425923</v>
       </c>
       <c r="D2" s="14">
-        <v>214.99998842592322</v>
+        <f>Indisp_Prog[[#This Row],[Fecha_Hora_Fin]]-Indisp_Prog[[#This Row],[Fecha_Hora_Inicio]]</f>
+        <v>272.99998842592322</v>
       </c>
       <c r="E2" t="s">
         <v>118</v>
@@ -11177,29 +11175,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -11402,25 +11377,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11439,6 +11419,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1412" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1717139-AF42-45E9-8CDD-DA50C4838550}"/>
+  <xr:revisionPtr revIDLastSave="1417" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBC94103-9703-4FF1-B4D3-8AF5E3FC20FA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DATOS_EVENTOS_GEN_CHILE" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="130">
   <si>
     <t>ID</t>
   </si>
@@ -534,16 +534,6 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -573,6 +563,16 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ h:mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -865,23 +865,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J353" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J353" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A10:J353" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="3" xr3:uid="{AFE823F6-980E-4E32-B4F4-6ECDE10F377D}" name="ID"/>
-    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{CD000998-6E2C-4963-8605-37081D9C1A64}" name="Unidad" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{542F6635-555D-4F04-8C27-263AF6E0C9F1}" name="Sitio" dataDxfId="6">
       <calculatedColumnFormula>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{6D2AC534-BC70-4E36-815D-053C7EC9A0CE}" name="Carga_Disponible" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{FBB18F6C-27E4-42D9-9835-9152B6D0D871}" name="Estado_Op" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{21A32989-F167-49C0-9D41-2BD3A8923998}" name="Fecha_Hora_Inicio" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{713F74B7-95D9-4F96-AA1E-57E68B8A7FE7}" name="Fecha_Hora_Final" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{20481209-2CB3-4DCC-A330-D866983AA4F9}" name="Motivo" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{55FF6738-9798-4086-9AA1-DC8A3EF8081F}" name="Detalle" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{C2DE1A32-EBAC-4C95-A60E-FB6BAE643966}" name="Verificación"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -909,9 +909,9 @@
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1EEE0FFC-B699-4850-9A13-72CF6FB78CA6}" name="Unidad"/>
-    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{BDB3B76C-8D9D-4A32-9C94-204172B9E68C}" name="Fecha_Hora_Inicio" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{A21A7F07-F50E-4006-B601-758B5E8BD7BE}" name="Fecha_Hora_Fin" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{F49EC928-7A7A-47BB-9275-EDE8B8DF6BC7}" name="Días_de_Mantenimiento" dataDxfId="9"/>
     <tableColumn id="5" xr3:uid="{E5C19B72-F1F0-4F1D-9466-99048BCEFC0C}" name="Motivo"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1266,7 +1266,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10662,11 +10662,23 @@
         <v>23</v>
       </c>
     </row>
-    <row r="353" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B353" s="13"/>
-      <c r="C353" s="13"/>
-      <c r="D353" s="14"/>
-      <c r="E353" s="13"/>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>343</v>
+      </c>
+      <c r="B353" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C353" s="13" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D353" s="14">
+        <v>0</v>
+      </c>
+      <c r="E353" s="13" t="s">
+        <v>13</v>
+      </c>
       <c r="F353" s="15"/>
       <c r="G353" s="15"/>
       <c r="H353" s="11"/>
@@ -11175,6 +11187,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FB7AAE8C8816FD47B559A0CCF555AFF0" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c9910934a78ddf693a6b708b52e9b37">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f95d585e-e7a7-414c-955d-38a47c8579bd" xmlns:ns3="33ab045e-9213-4eea-a9f2-a5b809105d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a9c61c95b4e11caed4e46447c2ca01e7" ns2:_="" ns3:_="">
     <xsd:import namespace="f95d585e-e7a7-414c-955d-38a47c8579bd"/>
@@ -11377,30 +11412,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="33ab045e-9213-4eea-a9f2-a5b809105d1e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8D88B3-F603-4313-AC14-F1B2905698D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11419,24 +11449,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3DCBC87-226F-4D83-ADFE-2178829A4AE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="33ab045e-9213-4eea-a9f2-a5b809105d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59A15667-1AA5-4404-9771-E51F1A78CCAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0a9b9e15-83d2-4075-9282-a04e05c6580a}" enabled="1" method="Standard" siteId="{24139d14-c62c-4c47-8bdd-ce71ea1d50cf}" contentBits="0" removed="0"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1417" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBC94103-9703-4FF1-B4D3-8AF5E3FC20FA}"/>
+  <xr:revisionPtr revIDLastSave="1419" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79A36A9C-0BDC-45C9-978F-A3DD19003660}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="130">
   <si>
     <t>ID</t>
   </si>
@@ -10679,9 +10679,13 @@
       <c r="E353" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F353" s="15"/>
+      <c r="F353" s="15">
+        <v>46299.243055555555</v>
+      </c>
       <c r="G353" s="15"/>
-      <c r="H353" s="11"/>
+      <c r="H353" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="I353" s="11"/>
     </row>
   </sheetData>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1419" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79A36A9C-0BDC-45C9-978F-A3DD19003660}"/>
+  <xr:revisionPtr revIDLastSave="1426" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99269D43-84B6-4D22-B0A4-212BFE969FEE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="131">
   <si>
     <t>ID</t>
   </si>
@@ -444,6 +444,9 @@
   </si>
   <si>
     <t>Falla valvúla control nivel del Domo MP</t>
+  </si>
+  <si>
+    <t>Falla en valvúla de gas, alimentación combustible a TG</t>
   </si>
 </sst>
 </file>
@@ -487,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -526,6 +529,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -865,8 +871,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J353" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A10:J353" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J354" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A10:J354" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1247,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J353"/>
+  <dimension ref="A9:J354"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -10662,8 +10668,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A353">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
         <v>343</v>
       </c>
       <c r="B353" s="13" t="s">
@@ -10682,11 +10688,34 @@
       <c r="F353" s="15">
         <v>46299.243055555555</v>
       </c>
-      <c r="G353" s="15"/>
+      <c r="G353" s="15">
+        <v>46299.673611111109</v>
+      </c>
       <c r="H353" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="I353" s="11"/>
+      <c r="I353" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="J353" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>344</v>
+      </c>
+      <c r="B354" s="13"/>
+      <c r="C354" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D354" s="14"/>
+      <c r="E354" s="13"/>
+      <c r="F354" s="15"/>
+      <c r="G354" s="15"/>
+      <c r="H354" s="11"/>
+      <c r="I354" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1426" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99269D43-84B6-4D22-B0A4-212BFE969FEE}"/>
+  <xr:revisionPtr revIDLastSave="1434" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B209E8A1-E8AC-4180-BB32-E5D7EEB967E8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="131">
   <si>
     <t>ID</t>
   </si>
@@ -871,8 +871,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J354" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A10:J354" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J355" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A10:J355" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1253,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J354"/>
+  <dimension ref="A9:J355"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -10702,7 +10702,7 @@
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A354">
+      <c r="A354" s="1">
         <v>344</v>
       </c>
       <c r="B354" s="13"/>
@@ -10710,12 +10710,40 @@
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
       </c>
-      <c r="D354" s="14"/>
-      <c r="E354" s="13"/>
-      <c r="F354" s="15"/>
-      <c r="G354" s="15"/>
-      <c r="H354" s="11"/>
-      <c r="I354" s="11"/>
+      <c r="D354" s="14">
+        <v>262</v>
+      </c>
+      <c r="E354" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F354" s="15">
+        <v>46298.354166666664</v>
+      </c>
+      <c r="G354" s="15">
+        <v>46298.465277777781</v>
+      </c>
+      <c r="H354" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I354" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>345</v>
+      </c>
+      <c r="B355" s="13"/>
+      <c r="C355" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D355" s="14"/>
+      <c r="E355" s="13"/>
+      <c r="F355" s="15"/>
+      <c r="G355" s="15"/>
+      <c r="H355" s="11"/>
+      <c r="I355" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1434" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B209E8A1-E8AC-4180-BB32-E5D7EEB967E8}"/>
+  <xr:revisionPtr revIDLastSave="1442" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{653E942F-C15D-4EE1-9600-A2D4E938D2CB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="131">
   <si>
     <t>ID</t>
   </si>
@@ -871,8 +871,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J355" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="A10:J355" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}" name="BD_GEN_CL" displayName="BD_GEN_CL" ref="A10:J356" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A10:J356" xr:uid="{BF87FAA9-1AA2-4036-9224-EC7F4966CB13}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I308">
     <sortCondition ref="F10:F308"/>
   </sortState>
@@ -1253,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE341A5-48DC-491A-A7A3-9CB9E0074F67}">
-  <dimension ref="A9:J355"/>
+  <dimension ref="A9:J356"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1272,7 +1272,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10730,20 +10730,46 @@
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A355">
+      <c r="A355" s="1">
         <v>345</v>
       </c>
-      <c r="B355" s="13"/>
+      <c r="B355" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="C355" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CET</v>
-      </c>
-      <c r="D355" s="14"/>
-      <c r="E355" s="13"/>
-      <c r="F355" s="15"/>
-      <c r="G355" s="15"/>
+        <v>CEM</v>
+      </c>
+      <c r="D355" s="14">
+        <v>70</v>
+      </c>
+      <c r="E355" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F355" s="15">
+        <v>46298.188194444447</v>
+      </c>
+      <c r="G355" s="15">
+        <v>46298.261111111111</v>
+      </c>
       <c r="H355" s="11"/>
       <c r="I355" s="11"/>
+    </row>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
+        <v>346</v>
+      </c>
+      <c r="B356" s="13"/>
+      <c r="C356" s="16" t="str">
+        <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
+        <v>CET</v>
+      </c>
+      <c r="D356" s="14"/>
+      <c r="E356" s="13"/>
+      <c r="F356" s="15"/>
+      <c r="G356" s="15"/>
+      <c r="H356" s="11"/>
+      <c r="I356" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Base_Dato_Indisponibilidad_GEN_CL.xlsx
+++ b/Base_Dato_Indisponibilidad_GEN_CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie.sharepoint.com/sites/OperacionesCentralMejillones-Administracin/Shared Documents/Administración/0.- Gerencia/02.- Operación/05.- EFOF_GEN_CL/05.- PRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1442" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{653E942F-C15D-4EE1-9600-A2D4E938D2CB}"/>
+  <xr:revisionPtr revIDLastSave="1458" documentId="8_{55EF2082-D0B7-4F26-90F5-434FA2717943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{864561BD-096B-40D3-B3A8-2565C78A7703}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E052323F-F4D0-446A-B69C-8F538CB3C6F5}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="135">
   <si>
     <t>ID</t>
   </si>
@@ -447,6 +447,18 @@
   </si>
   <si>
     <t>Falla en valvúla de gas, alimentación combustible a TG</t>
+  </si>
+  <si>
+    <t>Alto consumo agua desmineralizada en caldera.</t>
+  </si>
+  <si>
+    <t>Posible rotura caldera.</t>
+  </si>
+  <si>
+    <t>Rotura caldera vortex derecho y SH2</t>
+  </si>
+  <si>
+    <t>Abierto</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1274,7 @@
     <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="151.28515625" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.7109375" customWidth="1"/>
@@ -1272,7 +1284,7 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>SUBTOTAL(103,BD_GEN_CL[Unidad])</f>
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10705,7 +10717,9 @@
       <c r="A354" s="1">
         <v>344</v>
       </c>
-      <c r="B354" s="13"/>
+      <c r="B354" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="C354" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
         <v>CET</v>
@@ -10727,6 +10741,9 @@
       </c>
       <c r="I354" s="11" t="s">
         <v>127</v>
+      </c>
+      <c r="J354" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.25">
@@ -10752,24 +10769,46 @@
       <c r="G355" s="15">
         <v>46298.261111111111</v>
       </c>
-      <c r="H355" s="11"/>
-      <c r="I355" s="11"/>
+      <c r="H355" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="I355" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="J355" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>346</v>
       </c>
-      <c r="B356" s="13"/>
+      <c r="B356" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="C356" s="16" t="str">
         <f>IF(OR(BD_GEN_CL[[#This Row],[Unidad]]="CTM3",BD_GEN_CL[[#This Row],[Unidad]]="CTA",BD_GEN_CL[[#This Row],[Unidad]]="CTH",BD_GEN_CL[[#This Row],[Unidad]]="IEM",BD_GEN_CL[[#This Row],[Unidad]]="CTM1",BD_GEN_CL[[#This Row],[Unidad]]="CTM2"),"CEM","CET")</f>
-        <v>CET</v>
-      </c>
-      <c r="D356" s="14"/>
-      <c r="E356" s="13"/>
-      <c r="F356" s="15"/>
+        <v>CEM</v>
+      </c>
+      <c r="D356" s="14">
+        <v>0</v>
+      </c>
+      <c r="E356" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F356" s="15">
+        <v>46298.261111111111</v>
+      </c>
       <c r="G356" s="15"/>
-      <c r="H356" s="11"/>
-      <c r="I356" s="11"/>
+      <c r="H356" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="I356" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J356" s="1" t="s">
+        <v>134</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
